--- a/99/food/2026-01-28-sm.xlsx
+++ b/99/food/2026-01-28-sm.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>28.01.2026</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
